--- a/artfynd/A 52884-2022 artfynd.xlsx
+++ b/artfynd/A 52884-2022 artfynd.xlsx
@@ -900,27 +900,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127070858</v>
+        <v>127069646</v>
       </c>
       <c r="B4" t="n">
-        <v>57654</v>
+        <v>58334</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659535</v>
+        <v>659566</v>
       </c>
       <c r="R4" t="n">
-        <v>6580391</v>
+        <v>6580289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,17 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hörs på håll, uppskattad plats</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,27 +1010,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127069646</v>
+        <v>127070858</v>
       </c>
       <c r="B5" t="n">
-        <v>58334</v>
+        <v>57654</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1050,7 +1045,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1059,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659566</v>
+        <v>659535</v>
       </c>
       <c r="R5" t="n">
-        <v>6580289</v>
+        <v>6580391</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,12 +1084,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>hörs på håll, uppskattad plats</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 52884-2022 artfynd.xlsx
+++ b/artfynd/A 52884-2022 artfynd.xlsx
@@ -900,27 +900,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127069646</v>
+        <v>127070858</v>
       </c>
       <c r="B4" t="n">
-        <v>58334</v>
+        <v>57654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659566</v>
+        <v>659535</v>
       </c>
       <c r="R4" t="n">
-        <v>6580289</v>
+        <v>6580391</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,12 +974,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>hörs på håll, uppskattad plats</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,27 +1015,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127070858</v>
+        <v>127069646</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>58334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1045,7 +1050,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1054,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659535</v>
+        <v>659566</v>
       </c>
       <c r="R5" t="n">
-        <v>6580391</v>
+        <v>6580289</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,17 +1089,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>hörs på håll, uppskattad plats</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 52884-2022 artfynd.xlsx
+++ b/artfynd/A 52884-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127069653</v>
       </c>
       <c r="B2" t="n">
-        <v>58334</v>
+        <v>58338</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127070692</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>127069646</v>
       </c>
       <c r="B4" t="n">
-        <v>58334</v>
+        <v>58338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>127070858</v>
       </c>
       <c r="B5" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>127069660</v>
       </c>
       <c r="B6" t="n">
-        <v>58027</v>
+        <v>58031</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127070205</v>
       </c>
       <c r="B7" t="n">
-        <v>58195</v>
+        <v>58199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52884-2022 artfynd.xlsx
+++ b/artfynd/A 52884-2022 artfynd.xlsx
@@ -900,27 +900,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127069646</v>
+        <v>127070858</v>
       </c>
       <c r="B4" t="n">
-        <v>58338</v>
+        <v>57658</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659566</v>
+        <v>659535</v>
       </c>
       <c r="R4" t="n">
-        <v>6580289</v>
+        <v>6580391</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,12 +974,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>hörs på håll, uppskattad plats</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,27 +1015,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127070858</v>
+        <v>127069646</v>
       </c>
       <c r="B5" t="n">
-        <v>57658</v>
+        <v>58338</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1045,7 +1050,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1054,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659535</v>
+        <v>659566</v>
       </c>
       <c r="R5" t="n">
-        <v>6580391</v>
+        <v>6580289</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,17 +1089,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>hörs på håll, uppskattad plats</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 52884-2022 artfynd.xlsx
+++ b/artfynd/A 52884-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127069653</v>
       </c>
       <c r="B2" t="n">
-        <v>58338</v>
+        <v>58340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127070692</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>127070858</v>
       </c>
       <c r="B4" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1018,7 +1018,7 @@
         <v>127069646</v>
       </c>
       <c r="B5" t="n">
-        <v>58338</v>
+        <v>58340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>127069660</v>
       </c>
       <c r="B6" t="n">
-        <v>58031</v>
+        <v>58033</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127070205</v>
       </c>
       <c r="B7" t="n">
-        <v>58199</v>
+        <v>58201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52884-2022 artfynd.xlsx
+++ b/artfynd/A 52884-2022 artfynd.xlsx
@@ -900,27 +900,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127070858</v>
+        <v>127069646</v>
       </c>
       <c r="B4" t="n">
-        <v>57660</v>
+        <v>58340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659535</v>
+        <v>659566</v>
       </c>
       <c r="R4" t="n">
-        <v>6580391</v>
+        <v>6580289</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,17 +974,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>hörs på håll, uppskattad plats</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,27 +1010,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127069646</v>
+        <v>127070858</v>
       </c>
       <c r="B5" t="n">
-        <v>58340</v>
+        <v>57660</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1050,7 +1045,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1059,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659566</v>
+        <v>659535</v>
       </c>
       <c r="R5" t="n">
-        <v>6580289</v>
+        <v>6580391</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,12 +1084,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>hörs på håll, uppskattad plats</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 52884-2022 artfynd.xlsx
+++ b/artfynd/A 52884-2022 artfynd.xlsx
@@ -900,27 +900,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127069646</v>
+        <v>127070858</v>
       </c>
       <c r="B4" t="n">
-        <v>58340</v>
+        <v>57660</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659566</v>
+        <v>659535</v>
       </c>
       <c r="R4" t="n">
-        <v>6580289</v>
+        <v>6580391</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,12 +974,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>hörs på håll, uppskattad plats</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,27 +1015,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127070858</v>
+        <v>127069646</v>
       </c>
       <c r="B5" t="n">
-        <v>57660</v>
+        <v>58340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1045,7 +1050,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1054,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659535</v>
+        <v>659566</v>
       </c>
       <c r="R5" t="n">
-        <v>6580391</v>
+        <v>6580289</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,17 +1089,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>hörs på håll, uppskattad plats</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 52884-2022 artfynd.xlsx
+++ b/artfynd/A 52884-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127069653</v>
       </c>
       <c r="B2" t="n">
-        <v>58340</v>
+        <v>58343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127070692</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -903,7 +903,7 @@
         <v>127069646</v>
       </c>
       <c r="B4" t="n">
-        <v>58340</v>
+        <v>58343</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1013,7 +1013,7 @@
         <v>127070858</v>
       </c>
       <c r="B5" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1128,7 +1128,7 @@
         <v>127069660</v>
       </c>
       <c r="B6" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127070205</v>
       </c>
       <c r="B7" t="n">
-        <v>58201</v>
+        <v>58204</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52884-2022 artfynd.xlsx
+++ b/artfynd/A 52884-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127069653</v>
       </c>
       <c r="B2" t="n">
-        <v>58343</v>
+        <v>58334</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -788,7 +788,7 @@
         <v>127070692</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,27 +900,27 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127069646</v>
+        <v>127070858</v>
       </c>
       <c r="B4" t="n">
-        <v>58343</v>
+        <v>57654</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -935,7 +935,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659566</v>
+        <v>659535</v>
       </c>
       <c r="R4" t="n">
-        <v>6580289</v>
+        <v>6580391</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,12 +974,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-06-17</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>hörs på håll, uppskattad plats</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1010,27 +1015,27 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127070858</v>
+        <v>127069646</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>58334</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103044</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1045,7 +1050,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1054,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659535</v>
+        <v>659566</v>
       </c>
       <c r="R5" t="n">
-        <v>6580391</v>
+        <v>6580289</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,17 +1089,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>hörs på håll, uppskattad plats</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1128,7 +1128,7 @@
         <v>127069660</v>
       </c>
       <c r="B6" t="n">
-        <v>58036</v>
+        <v>58027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>127070205</v>
       </c>
       <c r="B7" t="n">
-        <v>58204</v>
+        <v>58195</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 52884-2022 artfynd.xlsx
+++ b/artfynd/A 52884-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127069653</v>
+        <v>127070692</v>
       </c>
       <c r="B2" t="n">
-        <v>58343</v>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103044</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>659615</v>
+        <v>659518</v>
       </c>
       <c r="R2" t="n">
-        <v>6580361</v>
+        <v>6580309</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,12 +749,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>hör vagt en spillkråka från norr, samtidigt två i söder där jag står, två revir?</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,14 +790,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127070692</v>
+        <v>127070858</v>
       </c>
       <c r="B3" t="n">
-        <v>57663</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -829,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>659518</v>
+        <v>659535</v>
       </c>
       <c r="R3" t="n">
-        <v>6580309</v>
+        <v>6580391</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -859,17 +864,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-05-26</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>hör vagt en spillkråka från norr, samtidigt två i söder där jag står, två revir?</t>
+          <t>hörs på håll, uppskattad plats</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,10 +905,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127069646</v>
+        <v>93951977</v>
       </c>
       <c r="B4" t="n">
-        <v>58343</v>
+        <v>5173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,16 +916,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103044</v>
+        <v>102185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Myskbock</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Aromia moschata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -928,29 +933,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lovö, Upl</t>
+          <t>Vattenverket, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>659566</v>
+        <v>659535</v>
       </c>
       <c r="R4" t="n">
-        <v>6580289</v>
+        <v>6580230</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,12 +970,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-03-20</t>
+          <t>2021-05-19</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,26 +990,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marlijn Sterenborg</t>
+          <t>Ann-Sofie Frydenlund</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Edwin Sahlin</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Lovö inventering 2025</t>
-        </is>
-      </c>
+          <t>Ann-Sofie Frydenlund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127070858</v>
+        <v>127070205</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>58497</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,16 +1013,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>102990</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1045,7 +1037,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1054,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>659535</v>
+        <v>659594</v>
       </c>
       <c r="R5" t="n">
-        <v>6580391</v>
+        <v>6580490</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,17 +1076,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>hörs på håll, uppskattad plats</t>
+          <t>2025-04-15</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1125,10 +1112,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127069660</v>
+        <v>127069642</v>
       </c>
       <c r="B6" t="n">
-        <v>58036</v>
+        <v>58327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1160,7 +1147,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>obs i häcktid, lämplig biotop</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1169,10 +1156,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>659623</v>
+        <v>659546</v>
       </c>
       <c r="R6" t="n">
-        <v>6580287</v>
+        <v>6580228</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,10 +1222,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127070205</v>
+        <v>127069660</v>
       </c>
       <c r="B7" t="n">
-        <v>58204</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,16 +1233,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102990</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1265,12 +1252,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>obs i häcktid, lämplig biotop</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1279,10 +1266,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>659594</v>
+        <v>659623</v>
       </c>
       <c r="R7" t="n">
-        <v>6580490</v>
+        <v>6580287</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,12 +1296,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-04-15</t>
+          <t>2025-03-20</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1342,6 +1329,983 @@
           <t>Lovö inventering 2025</t>
         </is>
       </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127070203</v>
+      </c>
+      <c r="B8" t="n">
+        <v>58327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lovö, Upl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>659582</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6580513</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lovö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Edwin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Lovö inventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127070676</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lovö, Upl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>659596</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6580258</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lovö</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Edwin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Lovö inventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>127070677</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58439</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>103018</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svartvit flugsnappare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Ficedula hypoleuca</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Pallas, 1764)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lovö, Upl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>659611</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6580491</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lovö</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-05-26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Edwin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Lovö inventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>127069646</v>
+      </c>
+      <c r="B11" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lovö, Upl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>659566</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6580289</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lovö</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Edwin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Lovö inventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127069651</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lovö, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>659573</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6580256</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lovö</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Edwin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Lovö inventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127069653</v>
+      </c>
+      <c r="B13" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lovö, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>659615</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6580361</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lovö</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-03-20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Edwin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Lovö inventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127070195</v>
+      </c>
+      <c r="B14" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Lovö, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>659429</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6580288</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lovö</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Edwin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Lovö inventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127070199</v>
+      </c>
+      <c r="B15" t="n">
+        <v>58636</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>obs i häcktid, lämplig biotop</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lovö, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>659507</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6580461</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lovö</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-04-15</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Marlijn Sterenborg</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Edwin Sahlin</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Lovö inventering 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>93951974</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Vattenverket, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>659571</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6580244</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Ekerö</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lovö</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-05-19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-05-19</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Ann-Sofie Frydenlund</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Ann-Sofie Frydenlund</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
